--- a/Model Files/L-Shaped/data/production_capacity_scenarios_NEW_23JUN.xlsx
+++ b/Model Files/L-Shaped/data/production_capacity_scenarios_NEW_23JUN.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5e6b18ad1acc1266/Desktop/Vaccine_Tender/Model Files/L-Shaped/data_generation_codes/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5e6b18ad1acc1266/Desktop/Vaccine_Tender/Model Files/L-Shaped/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="30" documentId="8_{4F78CD46-C400-4EB4-A62E-78EA7D017647}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A4C87393-2BEA-468F-9851-D4371EEDFF6A}"/>
+  <xr:revisionPtr revIDLastSave="36" documentId="8_{4F78CD46-C400-4EB4-A62E-78EA7D017647}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C4A518E5-2493-4A96-8DA6-F9B9EF107FEE}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-2565" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="base_capacity" sheetId="1" r:id="rId1"/>
@@ -164,10 +164,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -459,6 +455,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
